--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.97122500833317</v>
+        <v>3.407824063854141</v>
       </c>
       <c r="D2" t="n">
-        <v>21.37274814574169</v>
+        <v>3.473071573683025</v>
       </c>
       <c r="E2" t="n">
-        <v>13.71659227541958</v>
+        <v>2.228946244755682</v>
       </c>
       <c r="F2" t="n">
-        <v>10.53717989309326</v>
+        <v>1.712291732627654</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.96758055540849</v>
+        <v>9.09473184025388</v>
       </c>
       <c r="D3" t="n">
-        <v>49.40239516541775</v>
+        <v>8.027889214380385</v>
       </c>
       <c r="E3" t="n">
-        <v>13.71659227541958</v>
+        <v>2.228946244755682</v>
       </c>
       <c r="F3" t="n">
-        <v>10.53717989309326</v>
+        <v>1.712291732627654</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.20986256943627</v>
+        <v>4.259102667533394</v>
       </c>
       <c r="D4" t="n">
-        <v>30.39443642516162</v>
+        <v>4.939095919088763</v>
       </c>
       <c r="E4" t="n">
-        <v>13.71659227541958</v>
+        <v>2.228946244755682</v>
       </c>
       <c r="F4" t="n">
-        <v>10.53717989309326</v>
+        <v>1.712291732627654</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.22636934924472</v>
+        <v>8.324285019252267</v>
       </c>
       <c r="D5" t="n">
-        <v>45.98047014359165</v>
+        <v>7.471826398333643</v>
       </c>
       <c r="E5" t="n">
-        <v>13.71659227541958</v>
+        <v>2.228946244755682</v>
       </c>
       <c r="F5" t="n">
-        <v>10.53717989309326</v>
+        <v>1.712291732627654</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.2094972483812</v>
+        <v>5.559043302861946</v>
       </c>
       <c r="D6" t="n">
-        <v>30.36210549824351</v>
+        <v>4.933842143464571</v>
       </c>
       <c r="E6" t="n">
-        <v>13.71659227541958</v>
+        <v>2.228946244755682</v>
       </c>
       <c r="F6" t="n">
-        <v>10.53717989309326</v>
+        <v>1.712291732627654</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
